--- a/backend/server/hopmap_words_db.xlsx
+++ b/backend/server/hopmap_words_db.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex\Desktop\Working\Game Changers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex\Desktop\Working\Game Changers\dashbord-parents\game-changers-repo\backend\server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029CA8F0-D87A-4AD6-803B-3971D4BB5AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195D4FC8-6585-4506-8D1E-7C2BF2364991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14303" yWindow="-1470" windowWidth="19394" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>בוא לדיסקורד שלי</t>
   </si>
@@ -282,6 +282,18 @@
   </si>
   <si>
     <t>word</t>
+  </si>
+  <si>
+    <t>טלגרם</t>
+  </si>
+  <si>
+    <t>דיסקורד</t>
+  </si>
+  <si>
+    <t>telegram</t>
+  </si>
+  <si>
+    <t>discord</t>
   </si>
 </sst>
 </file>
@@ -359,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -368,6 +380,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -672,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A83"/>
+  <dimension ref="A1:A87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1093,6 +1108,26 @@
         <v>70</v>
       </c>
     </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
